--- a/scenarios/03_raj_mission_planner/3.4_off_nadir_agility/outputs/off_nadir_results.xlsx
+++ b/scenarios/03_raj_mission_planner/3.4_off_nadir_agility/outputs/off_nadir_results.xlsx
@@ -608,7 +608,7 @@
         <v>5.86</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>15374</v>
@@ -649,10 +649,10 @@
         <v>0.6457000000000001</v>
       </c>
       <c r="L4" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>5.85</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>5.89</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>16005</v>
@@ -693,10 +693,10 @@
         <v>0.6457000000000001</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5.82</v>
+        <v>5.79</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5.9</v>
+        <v>5.81</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>16623</v>
@@ -737,10 +737,10 @@
         <v>0.6457000000000001</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5.78</v>
+        <v>5.72</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5.91</v>
+        <v>5.76</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>17219</v>
@@ -781,10 +781,10 @@
         <v>0.6457000000000001</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5.92</v>
+        <v>5.68</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>17789</v>
@@ -825,10 +825,10 @@
         <v>0.6457000000000001</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>5.62</v>
+        <v>5.49</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5.93</v>
+        <v>5.57</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>18329</v>
@@ -869,10 +869,10 @@
         <v>0.6457000000000001</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5.5</v>
+        <v>5.32</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5.94</v>
+        <v>5.44</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>18837</v>
@@ -913,10 +913,10 @@
         <v>0.6457000000000001</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5.36</v>
+        <v>5.12</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5.95</v>
+        <v>5.27</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>19311</v>
@@ -957,10 +957,10 @@
         <v>0.6457000000000001</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5.19</v>
+        <v>4.86</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5.96</v>
+        <v>5.06</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>19754</v>

--- a/scenarios/03_raj_mission_planner/3.4_off_nadir_agility/outputs/off_nadir_results.xlsx
+++ b/scenarios/03_raj_mission_planner/3.4_off_nadir_agility/outputs/off_nadir_results.xlsx
@@ -555,16 +555,16 @@
         <v>85.8</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>5.86</v>
+        <v>5.65</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5.86</v>
+        <v>5.65</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>14737</v>
@@ -599,16 +599,16 @@
         <v>87.59999999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>5.86</v>
+        <v>5.65</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5.86</v>
+        <v>5.66</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>15374</v>
@@ -643,16 +643,16 @@
         <v>89.40000000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>5.84</v>
+        <v>5.63</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5.85</v>
+        <v>5.64</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>16005</v>
@@ -687,16 +687,16 @@
         <v>91.09999999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5.79</v>
+        <v>5.59</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5.81</v>
+        <v>5.61</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>16623</v>
@@ -731,16 +731,16 @@
         <v>92.7</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5.72</v>
+        <v>5.51</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5.76</v>
+        <v>5.55</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>17219</v>
@@ -775,16 +775,16 @@
         <v>94.3</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5.62</v>
+        <v>5.41</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5.68</v>
+        <v>5.47</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>17789</v>
@@ -819,16 +819,16 @@
         <v>95.7</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>5.49</v>
+        <v>5.28</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5.57</v>
+        <v>5.37</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>18329</v>
@@ -863,16 +863,16 @@
         <v>97</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5.32</v>
+        <v>5.11</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5.44</v>
+        <v>5.23</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>18837</v>
@@ -907,16 +907,16 @@
         <v>98.2</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5.12</v>
+        <v>4.91</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5.27</v>
+        <v>5.06</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>19311</v>
@@ -951,16 +951,16 @@
         <v>99.3</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.3809</v>
+        <v>0.2557</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5592</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4.86</v>
+        <v>4.65</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5.06</v>
+        <v>4.85</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>19754</v>
